--- a/raw_data/Planulae/Prot/liel12012026_562.xlsx
+++ b/raw_data/Planulae/Prot/liel12012026_562.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\Stylophora-pistillata-FPs\Raw_Data\Prot\Planulae\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\raw_data\Planulae\Prot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936D03CE-CA80-4415-8E04-000E710D9868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C3826D-8977-405D-AA33-4F5C741A91F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5280" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,6 @@
     <sheet name="calculates" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">calculates!$B$2:$B$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">calculates!$K$2:$K$13</definedName>
     <definedName name="MethodPointer1">1447419168</definedName>
     <definedName name="MethodPointer2">541</definedName>
   </definedNames>
@@ -243,7 +241,7 @@
     <t>notes</t>
   </si>
   <si>
-    <t>not sure if the number in the vile was correct</t>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -251,7 +249,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -467,7 +465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3430,7 +3428,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G2" s="23">
-        <f>AVERAGE(D2:F2)</f>
+        <f t="shared" ref="G2:G13" si="0">AVERAGE(D2:F2)</f>
         <v>0.67499999999999993</v>
       </c>
       <c r="H2" s="23">
@@ -3470,7 +3468,7 @@
         <v>0.69799999999999995</v>
       </c>
       <c r="G3" s="23">
-        <f>AVERAGE(D3:F3)</f>
+        <f t="shared" si="0"/>
         <v>0.76333333333333331</v>
       </c>
       <c r="H3" s="23">
@@ -3478,15 +3476,15 @@
         <v>0.68699999999999994</v>
       </c>
       <c r="I3" s="23">
-        <f t="shared" ref="I3:I13" si="0">(-0.0068449 + SQRT(0.0068449^2 - 4*(-0.000007514)*(-0.0094273 - H3))) / (2*-0.000007514)</f>
+        <f t="shared" ref="I3:I13" si="1">(-0.0068449 + SQRT(0.0068449^2 - 4*(-0.000007514)*(-0.0094273 - H3))) / (2*-0.000007514)</f>
         <v>116.69210586789144</v>
       </c>
       <c r="J3" s="23">
-        <f t="shared" ref="J3:J13" si="1">I3*4</f>
+        <f t="shared" ref="J3:J13" si="2">I3*4</f>
         <v>466.76842347156577</v>
       </c>
       <c r="K3" s="23">
-        <f t="shared" ref="K3:K13" si="2">J3/C3</f>
+        <f t="shared" ref="K3:K13" si="3">J3/C3</f>
         <v>46.67684234715658</v>
       </c>
     </row>
@@ -3510,7 +3508,7 @@
         <v>0.749</v>
       </c>
       <c r="G4" s="23">
-        <f>AVERAGE(D4:F4)</f>
+        <f t="shared" si="0"/>
         <v>0.78266666666666662</v>
       </c>
       <c r="H4" s="23">
@@ -3518,15 +3516,15 @@
         <v>0.70633333333333326</v>
       </c>
       <c r="I4" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>120.51099373374149</v>
       </c>
       <c r="J4" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>482.04397493496595</v>
       </c>
       <c r="K4" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48.204397493496593</v>
       </c>
     </row>
@@ -3550,7 +3548,7 @@
         <v>0.72</v>
       </c>
       <c r="G5" s="23">
-        <f>AVERAGE(D5:F5)</f>
+        <f t="shared" si="0"/>
         <v>0.65699999999999992</v>
       </c>
       <c r="H5" s="23">
@@ -3558,15 +3556,15 @@
         <v>0.58066666666666655</v>
       </c>
       <c r="I5" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>96.413511261178201</v>
       </c>
       <c r="J5" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>385.6540450447128</v>
       </c>
       <c r="K5" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38.565404504471282</v>
       </c>
     </row>
@@ -3590,7 +3588,7 @@
         <v>0.55600000000000005</v>
       </c>
       <c r="G6" s="23">
-        <f>AVERAGE(D6:F6)</f>
+        <f t="shared" si="0"/>
         <v>0.59466666666666668</v>
       </c>
       <c r="H6" s="23">
@@ -3598,15 +3596,15 @@
         <v>0.51833333333333331</v>
       </c>
       <c r="I6" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>85.041813315526582</v>
       </c>
       <c r="J6" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>340.16725326210633</v>
       </c>
       <c r="K6" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>34.016725326210633</v>
       </c>
     </row>
@@ -3630,7 +3628,7 @@
         <v>0.81200000000000006</v>
       </c>
       <c r="G7" s="23">
-        <f>AVERAGE(D7:F7)</f>
+        <f t="shared" si="0"/>
         <v>0.79800000000000004</v>
       </c>
       <c r="H7" s="23">
@@ -3638,15 +3636,15 @@
         <v>0.72166666666666668</v>
       </c>
       <c r="I7" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>123.57100925499157</v>
       </c>
       <c r="J7" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>494.28403701996626</v>
       </c>
       <c r="K7" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>49.428403701996629</v>
       </c>
     </row>
@@ -3670,7 +3668,7 @@
         <v>0.78200000000000003</v>
       </c>
       <c r="G8" s="23">
-        <f>AVERAGE(D8:F8)</f>
+        <f t="shared" si="0"/>
         <v>0.81199999999999994</v>
       </c>
       <c r="H8" s="23">
@@ -3678,15 +3676,15 @@
         <v>0.73566666666666658</v>
       </c>
       <c r="I8" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>126.38978535411813</v>
       </c>
       <c r="J8" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>505.55914141647253</v>
       </c>
       <c r="K8" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>50.55591414164725</v>
       </c>
     </row>
@@ -3710,7 +3708,7 @@
         <v>0.67800000000000005</v>
       </c>
       <c r="G9" s="23">
-        <f>AVERAGE(D9:F9)</f>
+        <f t="shared" si="0"/>
         <v>0.75266666666666671</v>
       </c>
       <c r="H9" s="23">
@@ -3718,15 +3716,15 @@
         <v>0.67633333333333334</v>
       </c>
       <c r="I9" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>114.60344695042532</v>
       </c>
       <c r="J9" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>458.41378780170129</v>
       </c>
       <c r="K9" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45.841378780170132</v>
       </c>
     </row>
@@ -3750,7 +3748,7 @@
         <v>0.69299999999999995</v>
       </c>
       <c r="G10" s="23">
-        <f>AVERAGE(D10:F10)</f>
+        <f t="shared" si="0"/>
         <v>0.76966666666666672</v>
       </c>
       <c r="H10" s="23">
@@ -3758,15 +3756,15 @@
         <v>0.69333333333333336</v>
       </c>
       <c r="I10" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>117.93836218040205</v>
       </c>
       <c r="J10" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>471.75344872160821</v>
       </c>
       <c r="K10" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47.175344872160821</v>
       </c>
     </row>
@@ -3790,7 +3788,7 @@
         <v>0.71499999999999997</v>
       </c>
       <c r="G11" s="23">
-        <f>AVERAGE(D11:F11)</f>
+        <f t="shared" si="0"/>
         <v>0.72533333333333327</v>
       </c>
       <c r="H11" s="23">
@@ -3798,15 +3796,15 @@
         <v>0.64899999999999991</v>
       </c>
       <c r="I11" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>109.30877613578561</v>
       </c>
       <c r="J11" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>437.23510454314243</v>
       </c>
       <c r="K11" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>43.723510454314244</v>
       </c>
     </row>
@@ -3830,7 +3828,7 @@
         <v>0.74199999999999999</v>
       </c>
       <c r="G12" s="23">
-        <f>AVERAGE(D12:F12)</f>
+        <f t="shared" si="0"/>
         <v>0.70766666666666678</v>
       </c>
       <c r="H12" s="23">
@@ -3838,15 +3836,15 @@
         <v>0.63133333333333341</v>
       </c>
       <c r="I12" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105.9292783903049</v>
       </c>
       <c r="J12" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>423.71711356121961</v>
       </c>
       <c r="K12" s="23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42.371711356121963</v>
       </c>
     </row>
@@ -3858,7 +3856,7 @@
         <v>39</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" s="12">
         <v>1.22</v>
@@ -3870,7 +3868,7 @@
         <v>0.90300000000000002</v>
       </c>
       <c r="G13" s="23">
-        <f>AVERAGE(D13:F13)</f>
+        <f t="shared" si="0"/>
         <v>1.0426666666666666</v>
       </c>
       <c r="H13" s="23">
@@ -3878,16 +3876,16 @@
         <v>0.96633333333333327</v>
       </c>
       <c r="I13" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>176.90907917729263</v>
       </c>
       <c r="J13" s="23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>707.6363167091705</v>
       </c>
       <c r="K13" s="23">
-        <f t="shared" si="2"/>
-        <v>70.76363167091705</v>
+        <f t="shared" si="3"/>
+        <v>50.545451193512179</v>
       </c>
       <c r="M13" t="s">
         <v>67</v>

--- a/raw_data/Planulae/Prot/liel12012026_562.xlsx
+++ b/raw_data/Planulae/Prot/liel12012026_562.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\MDPI_S_Pistillata_Bet-Hedging\raw_data\Planulae\Prot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C3826D-8977-405D-AA33-4F5C741A91F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CEABBE-2B6B-401F-98C1-BC71B531FA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="735" windowWidth="34665" windowHeight="13365" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -2797,7 +2797,7 @@
         <v>39</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="12:13" x14ac:dyDescent="0.2">
@@ -3856,7 +3856,7 @@
         <v>39</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" s="12">
         <v>1.22</v>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="K13" s="23">
         <f t="shared" si="3"/>
-        <v>50.545451193512179</v>
+        <v>47.175754447278031</v>
       </c>
       <c r="M13" t="s">
         <v>67</v>
